--- a/samples/스마트스토어_주문샘플.xlsx
+++ b/samples/스마트스토어_주문샘플.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>국내산 햇사과 5kg</t>
+          <t>[손칼국수] 쫄깃한 생칼국수 1kg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -676,7 +676,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>크기: 중과(18~20과)</t>
+          <t>4인분</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>제주 한라봉 3kg</t>
+          <t>감자 수제비 반죽 500g</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -815,7 +815,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>등급: 특품</t>
+          <t>2봉</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>국내산 햇사과 5kg</t>
+          <t>기장 쪽파 1단 (산지직송)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -954,7 +954,7 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>크기: 대과(14~16과)</t>
+          <t>1kg</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>유기농 고구마 10kg</t>
+          <t>옛날 구포국수 3kg</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>제주 한라봉 3kg</t>
+          <t>청도 한재 미나리 1kg</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1222,11 +1222,7 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>등급: 상품</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
         <v>1</v>
